--- a/logs/SM-S938N_grid_30m.xlsx
+++ b/logs/SM-S938N_grid_30m.xlsx
@@ -1157,7 +1157,7 @@
         <v>140</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.63</v>
+        <v>0.6245013819039954</v>
       </c>
       <c r="CK2" t="n">
         <v>3.77</v>
@@ -1439,7 +1439,7 @@
         <v>416</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.6</v>
+        <v>0.6044495401093971</v>
       </c>
       <c r="CK3" t="n">
         <v>6.29</v>
@@ -1721,7 +1721,7 @@
         <v>338</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.48</v>
+        <v>0.4786786551656995</v>
       </c>
       <c r="CK4" t="n">
         <v>4.49</v>
@@ -2003,7 +2003,7 @@
         <v>232</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.33</v>
+        <v>0.3255611696323961</v>
       </c>
       <c r="CK5" t="n">
         <v>2.53</v>
@@ -2285,7 +2285,7 @@
         <v>264</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.63</v>
+        <v>0.6272742380306796</v>
       </c>
       <c r="CK6" t="n">
         <v>5.2</v>
@@ -2567,7 +2567,7 @@
         <v>205</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.26</v>
+        <v>0.2614643655242993</v>
       </c>
       <c r="CK7" t="n">
         <v>1.91</v>
@@ -2849,7 +2849,7 @@
         <v>50</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.33</v>
+        <v>0.3326230298701519</v>
       </c>
       <c r="CK8" t="n">
         <v>1.2</v>
@@ -3131,7 +3131,7 @@
         <v>256</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.3</v>
+        <v>0.295225</v>
       </c>
       <c r="CK9" t="n">
         <v>2.41</v>
@@ -3413,7 +3413,7 @@
         <v>169</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.52</v>
+        <v>0.5201538461538462</v>
       </c>
       <c r="CK10" t="n">
         <v>3.45</v>
@@ -3695,7 +3695,7 @@
         <v>124</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0.54</v>
+        <v>0.5368402477580302</v>
       </c>
       <c r="CK11" t="n">
         <v>3.05</v>
@@ -3977,7 +3977,7 @@
         <v>58</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.44</v>
+        <v>0.4375130342885955</v>
       </c>
       <c r="CK12" t="n">
         <v>1.7</v>
@@ -4259,7 +4259,7 @@
         <v>109</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.61</v>
+        <v>0.6063806646478065</v>
       </c>
       <c r="CK13" t="n">
         <v>3.23</v>
@@ -4541,7 +4541,7 @@
         <v>241</v>
       </c>
       <c r="CJ14" t="n">
-        <v>0.44</v>
+        <v>0.4418914457109699</v>
       </c>
       <c r="CK14" t="n">
         <v>3.5</v>
@@ -4823,7 +4823,7 @@
         <v>746</v>
       </c>
       <c r="CJ15" t="n">
-        <v>0.26</v>
+        <v>0.2612089426926792</v>
       </c>
       <c r="CK15" t="n">
         <v>3.64</v>
@@ -5105,7 +5105,7 @@
         <v>467</v>
       </c>
       <c r="CJ16" t="n">
-        <v>0.65</v>
+        <v>0.6457696419718918</v>
       </c>
       <c r="CK16" t="n">
         <v>7.12</v>
@@ -5387,7 +5387,7 @@
         <v>356</v>
       </c>
       <c r="CJ17" t="n">
-        <v>0.42</v>
+        <v>0.4165579668848993</v>
       </c>
       <c r="CK17" t="n">
         <v>4.01</v>
@@ -5669,7 +5669,7 @@
         <v>256</v>
       </c>
       <c r="CJ18" t="n">
-        <v>0.32</v>
+        <v>0.3185</v>
       </c>
       <c r="CK18" t="n">
         <v>2.6</v>
@@ -5951,7 +5951,7 @@
         <v>129</v>
       </c>
       <c r="CJ19" t="n">
-        <v>0.4</v>
+        <v>0.4003586361243876</v>
       </c>
       <c r="CK19" t="n">
         <v>2.32</v>
@@ -6233,7 +6233,7 @@
         <v>389</v>
       </c>
       <c r="CJ20" t="n">
-        <v>0.33</v>
+        <v>0.3329094151015244</v>
       </c>
       <c r="CK20" t="n">
         <v>3.35</v>
@@ -6515,7 +6515,7 @@
         <v>44</v>
       </c>
       <c r="CJ21" t="n">
-        <v>0.41</v>
+        <v>0.4136735647606917</v>
       </c>
       <c r="CK21" t="n">
         <v>1.4</v>
@@ -6797,7 +6797,7 @@
         <v>109</v>
       </c>
       <c r="CJ22" t="n">
-        <v>0.64</v>
+        <v>0.6382954364713752</v>
       </c>
       <c r="CK22" t="n">
         <v>3.4</v>
@@ -7079,7 +7079,7 @@
         <v>476</v>
       </c>
       <c r="CJ23" t="n">
-        <v>0.16</v>
+        <v>0.1590105212945135</v>
       </c>
       <c r="CK23" t="n">
         <v>1.77</v>
@@ -7361,7 +7361,7 @@
         <v>197</v>
       </c>
       <c r="CJ24" t="n">
-        <v>0.19</v>
+        <v>0.1899161364477719</v>
       </c>
       <c r="CK24" t="n">
         <v>1.36</v>
@@ -7643,7 +7643,7 @@
         <v>41</v>
       </c>
       <c r="CJ25" t="n">
-        <v>1.18</v>
+        <v>1.181548212944438</v>
       </c>
       <c r="CK25" t="n">
         <v>3.86</v>
@@ -7925,7 +7925,7 @@
         <v>429</v>
       </c>
       <c r="CJ26" t="n">
-        <v>0.22</v>
+        <v>0.2195408847874128</v>
       </c>
       <c r="CK26" t="n">
         <v>2.32</v>
@@ -8207,7 +8207,7 @@
         <v>364</v>
       </c>
       <c r="CJ27" t="n">
-        <v>0.42</v>
+        <v>0.4232554856748418</v>
       </c>
       <c r="CK27" t="n">
         <v>4.12</v>
@@ -8489,7 +8489,7 @@
         <v>351</v>
       </c>
       <c r="CJ28" t="n">
-        <v>0.22</v>
+        <v>0.2165573152059999</v>
       </c>
       <c r="CK28" t="n">
         <v>2.07</v>
@@ -8771,7 +8771,7 @@
         <v>206</v>
       </c>
       <c r="CJ29" t="n">
-        <v>0.72</v>
+        <v>0.7210350618301093</v>
       </c>
       <c r="CK29" t="n">
         <v>5.28</v>
@@ -9053,7 +9053,7 @@
         <v>358</v>
       </c>
       <c r="CJ30" t="n">
-        <v>0.36</v>
+        <v>0.3635981580792993</v>
       </c>
       <c r="CK30" t="n">
         <v>3.51</v>
@@ -9335,7 +9335,7 @@
         <v>164</v>
       </c>
       <c r="CJ31" t="n">
-        <v>0.34</v>
+        <v>0.3367106306318347</v>
       </c>
       <c r="CK31" t="n">
         <v>2.2</v>
@@ -9617,7 +9617,7 @@
         <v>288</v>
       </c>
       <c r="CJ32" t="n">
-        <v>0.45</v>
+        <v>0.4458072553120787</v>
       </c>
       <c r="CK32" t="n">
         <v>3.86</v>
@@ -9899,7 +9899,7 @@
         <v>272</v>
       </c>
       <c r="CJ33" t="n">
-        <v>0.32</v>
+        <v>0.3244399056111026</v>
       </c>
       <c r="CK33" t="n">
         <v>2.73</v>
@@ -10181,7 +10181,7 @@
         <v>219</v>
       </c>
       <c r="CJ34" t="n">
-        <v>0.36</v>
+        <v>0.3589246659106709</v>
       </c>
       <c r="CK34" t="n">
         <v>2.71</v>
@@ -10463,7 +10463,7 @@
         <v>305</v>
       </c>
       <c r="CJ35" t="n">
-        <v>0.41</v>
+        <v>0.4152483120444173</v>
       </c>
       <c r="CK35" t="n">
         <v>3.7</v>
@@ -10745,7 +10745,7 @@
         <v>326</v>
       </c>
       <c r="CJ36" t="n">
-        <v>0.25</v>
+        <v>0.2529316588509231</v>
       </c>
       <c r="CK36" t="n">
         <v>2.33</v>
@@ -11027,7 +11027,7 @@
         <v>130</v>
       </c>
       <c r="CJ37" t="n">
-        <v>0.46</v>
+        <v>0.4607010363815964</v>
       </c>
       <c r="CK37" t="n">
         <v>2.68</v>
@@ -11309,7 +11309,7 @@
         <v>189</v>
       </c>
       <c r="CJ38" t="n">
-        <v>0.22</v>
+        <v>0.215279222647481</v>
       </c>
       <c r="CK38" t="n">
         <v>1.51</v>
@@ -11591,7 +11591,7 @@
         <v>211</v>
       </c>
       <c r="CJ39" t="n">
-        <v>0.28</v>
+        <v>0.2820078060161251</v>
       </c>
       <c r="CK39" t="n">
         <v>2.09</v>
@@ -11873,7 +11873,7 @@
         <v>395</v>
       </c>
       <c r="CJ40" t="n">
-        <v>0.25</v>
+        <v>0.2485181227123199</v>
       </c>
       <c r="CK40" t="n">
         <v>2.52</v>
@@ -12155,7 +12155,7 @@
         <v>194</v>
       </c>
       <c r="CJ41" t="n">
-        <v>0.3</v>
+        <v>0.3039547660324056</v>
       </c>
       <c r="CK41" t="n">
         <v>2.16</v>
@@ -12437,7 +12437,7 @@
         <v>134</v>
       </c>
       <c r="CJ42" t="n">
-        <v>0.42</v>
+        <v>0.4199091643065875</v>
       </c>
       <c r="CK42" t="n">
         <v>2.48</v>
@@ -12719,7 +12719,7 @@
         <v>103</v>
       </c>
       <c r="CJ43" t="n">
-        <v>0.27</v>
+        <v>0.2742368446986861</v>
       </c>
       <c r="CK43" t="n">
         <v>1.42</v>
@@ -13001,7 +13001,7 @@
         <v>131</v>
       </c>
       <c r="CJ44" t="n">
-        <v>0.32</v>
+        <v>0.3202300108474036</v>
       </c>
       <c r="CK44" t="n">
         <v>1.87</v>
@@ -13283,7 +13283,7 @@
         <v>123</v>
       </c>
       <c r="CJ45" t="n">
-        <v>0.33</v>
+        <v>0.3287126820143591</v>
       </c>
       <c r="CK45" t="n">
         <v>1.86</v>
@@ -13565,7 +13565,7 @@
         <v>232</v>
       </c>
       <c r="CJ46" t="n">
-        <v>0.32</v>
+        <v>0.3152667452961939</v>
       </c>
       <c r="CK46" t="n">
         <v>2.45</v>
@@ -13847,7 +13847,7 @@
         <v>156</v>
       </c>
       <c r="CJ47" t="n">
-        <v>0.34</v>
+        <v>0.3452362996037679</v>
       </c>
       <c r="CK47" t="n">
         <v>2.2</v>
@@ -14129,7 +14129,7 @@
         <v>78</v>
       </c>
       <c r="CJ48" t="n">
-        <v>0.67</v>
+        <v>0.6724366850377924</v>
       </c>
       <c r="CK48" t="n">
         <v>3.03</v>
@@ -14411,7 +14411,7 @@
         <v>342</v>
       </c>
       <c r="CJ49" t="n">
-        <v>0.23</v>
+        <v>0.2257473296455691</v>
       </c>
       <c r="CK49" t="n">
         <v>2.13</v>
@@ -14693,7 +14693,7 @@
         <v>165</v>
       </c>
       <c r="CJ50" t="n">
-        <v>0.31</v>
+        <v>0.3097491599029867</v>
       </c>
       <c r="CK50" t="n">
         <v>2.03</v>
@@ -14975,7 +14975,7 @@
         <v>172</v>
       </c>
       <c r="CJ51" t="n">
-        <v>0.38</v>
+        <v>0.3766104692934005</v>
       </c>
       <c r="CK51" t="n">
         <v>2.52</v>
@@ -15257,7 +15257,7 @@
         <v>203</v>
       </c>
       <c r="CJ52" t="n">
-        <v>0.23</v>
+        <v>0.2324849034772529</v>
       </c>
       <c r="CK52" t="n">
         <v>1.69</v>
@@ -15539,7 +15539,7 @@
         <v>117</v>
       </c>
       <c r="CJ53" t="n">
-        <v>0.19</v>
+        <v>0.1866381260232488</v>
       </c>
       <c r="CK53" t="n">
         <v>1.03</v>
@@ -15821,7 +15821,7 @@
         <v>189</v>
       </c>
       <c r="CJ54" t="n">
-        <v>0.29</v>
+        <v>0.2894151138903222</v>
       </c>
       <c r="CK54" t="n">
         <v>2.03</v>
@@ -16103,7 +16103,7 @@
         <v>121</v>
       </c>
       <c r="CJ55" t="n">
-        <v>0.37</v>
+        <v>0.3688363636363636</v>
       </c>
       <c r="CK55" t="n">
         <v>2.07</v>
@@ -16385,7 +16385,7 @@
         <v>194</v>
       </c>
       <c r="CJ56" t="n">
-        <v>0.32</v>
+        <v>0.3166195479504225</v>
       </c>
       <c r="CK56" t="n">
         <v>2.25</v>
@@ -16667,7 +16667,7 @@
         <v>168</v>
       </c>
       <c r="CJ57" t="n">
-        <v>0.24</v>
+        <v>0.2389233070813031</v>
       </c>
       <c r="CK57" t="n">
         <v>1.58</v>
@@ -16949,7 +16949,7 @@
         <v>130</v>
       </c>
       <c r="CJ58" t="n">
-        <v>0.71</v>
+        <v>0.7116799591864958</v>
       </c>
       <c r="CK58" t="n">
         <v>4.14</v>
@@ -17231,7 +17231,7 @@
         <v>256</v>
       </c>
       <c r="CJ59" t="n">
-        <v>0.42</v>
+        <v>0.420175</v>
       </c>
       <c r="CK59" t="n">
         <v>3.43</v>
@@ -17513,7 +17513,7 @@
         <v>146</v>
       </c>
       <c r="CJ60" t="n">
-        <v>0.34</v>
+        <v>0.339020476207074</v>
       </c>
       <c r="CK60" t="n">
         <v>2.09</v>
@@ -17795,7 +17795,7 @@
         <v>125</v>
       </c>
       <c r="CJ61" t="n">
-        <v>0.32</v>
+        <v>0.31906006757349</v>
       </c>
       <c r="CK61" t="n">
         <v>1.82</v>
@@ -18077,7 +18077,7 @@
         <v>139</v>
       </c>
       <c r="CJ62" t="n">
-        <v>0.17</v>
+        <v>0.1695699308216198</v>
       </c>
       <c r="CK62" t="n">
         <v>1.02</v>
@@ -18359,7 +18359,7 @@
         <v>219</v>
       </c>
       <c r="CJ63" t="n">
-        <v>0.36</v>
+        <v>0.3576002206490079</v>
       </c>
       <c r="CK63" t="n">
         <v>2.7</v>
@@ -18641,7 +18641,7 @@
         <v>497</v>
       </c>
       <c r="CJ64" t="n">
-        <v>0.14</v>
+        <v>0.1415480050953699</v>
       </c>
       <c r="CK64" t="n">
         <v>1.61</v>
@@ -18923,7 +18923,7 @@
         <v>88</v>
       </c>
       <c r="CJ65" t="n">
-        <v>0.36</v>
+        <v>0.359371127489017</v>
       </c>
       <c r="CK65" t="n">
         <v>1.72</v>
@@ -19205,7 +19205,7 @@
         <v>359</v>
       </c>
       <c r="CJ66" t="n">
-        <v>0.29</v>
+        <v>0.2896455619063296</v>
       </c>
       <c r="CK66" t="n">
         <v>2.8</v>
@@ -19487,7 +19487,7 @@
         <v>88</v>
       </c>
       <c r="CJ67" t="n">
-        <v>0.39</v>
+        <v>0.3928009998135766</v>
       </c>
       <c r="CK67" t="n">
         <v>1.88</v>
@@ -19769,7 +19769,7 @@
         <v>36</v>
       </c>
       <c r="CJ68" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8068666666666667</v>
       </c>
       <c r="CK68" t="n">
         <v>2.47</v>
@@ -20051,7 +20051,7 @@
         <v>160</v>
       </c>
       <c r="CJ69" t="n">
-        <v>0.51</v>
+        <v>0.5097907815957444</v>
       </c>
       <c r="CK69" t="n">
         <v>3.29</v>
@@ -20333,7 +20333,7 @@
         <v>110</v>
       </c>
       <c r="CJ70" t="n">
-        <v>0.79</v>
+        <v>0.786759190141893</v>
       </c>
       <c r="CK70" t="n">
         <v>4.21</v>
@@ -20615,7 +20615,7 @@
         <v>109</v>
       </c>
       <c r="CJ71" t="n">
-        <v>0.47</v>
+        <v>0.4655802007202973</v>
       </c>
       <c r="CK71" t="n">
         <v>2.48</v>
@@ -20897,7 +20897,7 @@
         <v>97</v>
       </c>
       <c r="CJ72" t="n">
-        <v>0.58</v>
+        <v>0.579112838745611</v>
       </c>
       <c r="CK72" t="n">
         <v>2.91</v>
@@ -21179,7 +21179,7 @@
         <v>181</v>
       </c>
       <c r="CJ73" t="n">
-        <v>0.59</v>
+        <v>0.5914837498176451</v>
       </c>
       <c r="CK73" t="n">
         <v>4.06</v>
@@ -21461,7 +21461,7 @@
         <v>71</v>
       </c>
       <c r="CJ74" t="n">
-        <v>0.46</v>
+        <v>0.4559140418117507</v>
       </c>
       <c r="CK74" t="n">
         <v>1.96</v>
@@ -21743,7 +21743,7 @@
         <v>124</v>
       </c>
       <c r="CJ75" t="n">
-        <v>0.41</v>
+        <v>0.4101107466479378</v>
       </c>
       <c r="CK75" t="n">
         <v>2.33</v>
@@ -22025,7 +22025,7 @@
         <v>767</v>
       </c>
       <c r="CJ76" t="n">
-        <v>0.08</v>
+        <v>0.08351036785011509</v>
       </c>
       <c r="CK76" t="n">
         <v>1.18</v>
@@ -22307,7 +22307,7 @@
         <v>287</v>
       </c>
       <c r="CJ77" t="n">
-        <v>0.28</v>
+        <v>0.2834530975956788</v>
       </c>
       <c r="CK77" t="n">
         <v>2.45</v>
@@ -22589,7 +22589,7 @@
         <v>139</v>
       </c>
       <c r="CJ78" t="n">
-        <v>0.53</v>
+        <v>0.5286591960909324</v>
       </c>
       <c r="CK78" t="n">
         <v>3.18</v>
@@ -22871,7 +22871,7 @@
         <v>169</v>
       </c>
       <c r="CJ79" t="n">
-        <v>0.33</v>
+        <v>0.3332</v>
       </c>
       <c r="CK79" t="n">
         <v>2.21</v>
@@ -23153,7 +23153,7 @@
         <v>145</v>
       </c>
       <c r="CJ80" t="n">
-        <v>0.26</v>
+        <v>0.2620583162264619</v>
       </c>
       <c r="CK80" t="n">
         <v>1.61</v>
@@ -23435,7 +23435,7 @@
         <v>176</v>
       </c>
       <c r="CJ81" t="n">
-        <v>0.43</v>
+        <v>0.4254928094681401</v>
       </c>
       <c r="CK81" t="n">
         <v>2.88</v>
@@ -23717,7 +23717,7 @@
         <v>117</v>
       </c>
       <c r="CJ82" t="n">
-        <v>0.53</v>
+        <v>0.5291100271727052</v>
       </c>
       <c r="CK82" t="n">
         <v>2.92</v>
@@ -23999,7 +23999,7 @@
         <v>407</v>
       </c>
       <c r="CJ83" t="n">
-        <v>0.3</v>
+        <v>0.2963184587443533</v>
       </c>
       <c r="CK83" t="n">
         <v>3.05</v>
@@ -24281,7 +24281,7 @@
         <v>265</v>
       </c>
       <c r="CJ84" t="n">
-        <v>0.35</v>
+        <v>0.353981418124396</v>
       </c>
       <c r="CK84" t="n">
         <v>2.94</v>
@@ -24563,7 +24563,7 @@
         <v>234</v>
       </c>
       <c r="CJ85" t="n">
-        <v>0.32</v>
+        <v>0.3216043128086033</v>
       </c>
       <c r="CK85" t="n">
         <v>2.51</v>
@@ -24845,7 +24845,7 @@
         <v>285</v>
       </c>
       <c r="CJ86" t="n">
-        <v>0.26</v>
+        <v>0.2635478626925754</v>
       </c>
       <c r="CK86" t="n">
         <v>2.27</v>
@@ -25127,7 +25127,7 @@
         <v>114</v>
       </c>
       <c r="CJ87" t="n">
-        <v>0.4</v>
+        <v>0.4001843855726262</v>
       </c>
       <c r="CK87" t="n">
         <v>2.18</v>
@@ -25409,7 +25409,7 @@
         <v>524</v>
       </c>
       <c r="CJ88" t="n">
-        <v>0.29</v>
+        <v>0.2868370418018187</v>
       </c>
       <c r="CK88" t="n">
         <v>3.35</v>
@@ -25691,7 +25691,7 @@
         <v>136</v>
       </c>
       <c r="CJ89" t="n">
-        <v>0.39</v>
+        <v>0.3932805554488012</v>
       </c>
       <c r="CK89" t="n">
         <v>2.34</v>
@@ -25973,7 +25973,7 @@
         <v>142</v>
       </c>
       <c r="CJ90" t="n">
-        <v>0.4</v>
+        <v>0.4013300927918086</v>
       </c>
       <c r="CK90" t="n">
         <v>2.44</v>
@@ -26255,7 +26255,7 @@
         <v>136</v>
       </c>
       <c r="CJ91" t="n">
-        <v>0.52</v>
+        <v>0.5210127016629418</v>
       </c>
       <c r="CK91" t="n">
         <v>3.1</v>
@@ -26537,7 +26537,7 @@
         <v>94</v>
       </c>
       <c r="CJ92" t="n">
-        <v>0.62</v>
+        <v>0.6206267922988411</v>
       </c>
       <c r="CK92" t="n">
         <v>3.07</v>
@@ -26819,7 +26819,7 @@
         <v>50</v>
       </c>
       <c r="CJ93" t="n">
-        <v>0.55</v>
+        <v>0.5543717164502532</v>
       </c>
       <c r="CK93" t="n">
         <v>2</v>
@@ -27101,7 +27101,7 @@
         <v>160</v>
       </c>
       <c r="CJ94" t="n">
-        <v>0.34</v>
+        <v>0.3455420799265988</v>
       </c>
       <c r="CK94" t="n">
         <v>2.23</v>
@@ -27383,7 +27383,7 @@
         <v>213</v>
       </c>
       <c r="CJ95" t="n">
-        <v>0.33</v>
+        <v>0.3303705883304427</v>
       </c>
       <c r="CK95" t="n">
         <v>2.46</v>
@@ -27665,7 +27665,7 @@
         <v>234</v>
       </c>
       <c r="CJ96" t="n">
-        <v>0.24</v>
+        <v>0.2370390353370184</v>
       </c>
       <c r="CK96" t="n">
         <v>1.85</v>
@@ -27947,7 +27947,7 @@
         <v>315</v>
       </c>
       <c r="CJ97" t="n">
-        <v>0.25</v>
+        <v>0.2462666811044933</v>
       </c>
       <c r="CK97" t="n">
         <v>2.23</v>
@@ -28229,7 +28229,7 @@
         <v>328</v>
       </c>
       <c r="CJ98" t="n">
-        <v>0.23</v>
+        <v>0.2337614543952352</v>
       </c>
       <c r="CK98" t="n">
         <v>2.16</v>
@@ -28511,7 +28511,7 @@
         <v>360</v>
       </c>
       <c r="CJ99" t="n">
-        <v>0.2</v>
+        <v>0.1952390227387957</v>
       </c>
       <c r="CK99" t="n">
         <v>1.89</v>
@@ -28793,7 +28793,7 @@
         <v>225</v>
       </c>
       <c r="CJ100" t="n">
-        <v>0.35</v>
+        <v>0.3501866666666667</v>
       </c>
       <c r="CK100" t="n">
         <v>2.68</v>
@@ -29075,7 +29075,7 @@
         <v>525</v>
       </c>
       <c r="CJ101" t="n">
-        <v>0.25</v>
+        <v>0.246359269360826</v>
       </c>
       <c r="CK101" t="n">
         <v>2.88</v>
@@ -29357,7 +29357,7 @@
         <v>439</v>
       </c>
       <c r="CJ102" t="n">
-        <v>0.28</v>
+        <v>0.2787661745003473</v>
       </c>
       <c r="CK102" t="n">
         <v>2.98</v>
@@ -29639,7 +29639,7 @@
         <v>300</v>
       </c>
       <c r="CJ103" t="n">
-        <v>0.27</v>
+        <v>0.2727171731544116</v>
       </c>
       <c r="CK103" t="n">
         <v>2.41</v>
@@ -29921,7 +29921,7 @@
         <v>677</v>
       </c>
       <c r="CJ104" t="n">
-        <v>0.23</v>
+        <v>0.2282466255346326</v>
       </c>
       <c r="CK104" t="n">
         <v>3.03</v>
@@ -30203,7 +30203,7 @@
         <v>248</v>
       </c>
       <c r="CJ105" t="n">
-        <v>0.24</v>
+        <v>0.2389634389635584</v>
       </c>
       <c r="CK105" t="n">
         <v>1.92</v>
@@ -30485,7 +30485,7 @@
         <v>366</v>
       </c>
       <c r="CJ106" t="n">
-        <v>0.26</v>
+        <v>0.2581761198338433</v>
       </c>
       <c r="CK106" t="n">
         <v>2.52</v>
@@ -30767,7 +30767,7 @@
         <v>317</v>
       </c>
       <c r="CJ107" t="n">
-        <v>0.25</v>
+        <v>0.2531945051008201</v>
       </c>
       <c r="CK107" t="n">
         <v>2.3</v>
@@ -31049,7 +31049,7 @@
         <v>343</v>
       </c>
       <c r="CJ108" t="n">
-        <v>0.23</v>
+        <v>0.2307095143248323</v>
       </c>
       <c r="CK108" t="n">
         <v>2.18</v>
@@ -31331,7 +31331,7 @@
         <v>522</v>
       </c>
       <c r="CJ109" t="n">
-        <v>0.22</v>
+        <v>0.2161829110602472</v>
       </c>
       <c r="CK109" t="n">
         <v>2.52</v>
@@ -31613,7 +31613,7 @@
         <v>591</v>
       </c>
       <c r="CJ110" t="n">
-        <v>0.31</v>
+        <v>0.3087884907948762</v>
       </c>
       <c r="CK110" t="n">
         <v>3.83</v>
@@ -31895,7 +31895,7 @@
         <v>148</v>
       </c>
       <c r="CJ111" t="n">
-        <v>0.44</v>
+        <v>0.4398330506367529</v>
       </c>
       <c r="CK111" t="n">
         <v>2.73</v>
@@ -32177,7 +32177,7 @@
         <v>409</v>
       </c>
       <c r="CJ112" t="n">
-        <v>0.33</v>
+        <v>0.3304827504015277</v>
       </c>
       <c r="CK112" t="n">
         <v>3.41</v>
@@ -32459,7 +32459,7 @@
         <v>151</v>
       </c>
       <c r="CJ113" t="n">
-        <v>0.32</v>
+        <v>0.3190050758382945</v>
       </c>
       <c r="CK113" t="n">
         <v>2</v>
@@ -32741,7 +32741,7 @@
         <v>549</v>
       </c>
       <c r="CJ114" t="n">
-        <v>0.22</v>
+        <v>0.2149824571993278</v>
       </c>
       <c r="CK114" t="n">
         <v>2.57</v>
@@ -33023,7 +33023,7 @@
         <v>457</v>
       </c>
       <c r="CJ115" t="n">
-        <v>0.27</v>
+        <v>0.273221099940971</v>
       </c>
       <c r="CK115" t="n">
         <v>2.98</v>
@@ -33305,7 +33305,7 @@
         <v>499</v>
       </c>
       <c r="CJ116" t="n">
-        <v>0.25</v>
+        <v>0.2509411198094534</v>
       </c>
       <c r="CK116" t="n">
         <v>2.86</v>
@@ -33587,7 +33587,7 @@
         <v>763</v>
       </c>
       <c r="CJ117" t="n">
-        <v>0.16</v>
+        <v>0.161071854727389</v>
       </c>
       <c r="CK117" t="n">
         <v>2.27</v>
@@ -33869,7 +33869,7 @@
         <v>507</v>
       </c>
       <c r="CJ118" t="n">
-        <v>0.33</v>
+        <v>0.3325182258058897</v>
       </c>
       <c r="CK118" t="n">
         <v>3.82</v>
@@ -34151,7 +34151,7 @@
         <v>327</v>
       </c>
       <c r="CJ119" t="n">
-        <v>0.32</v>
+        <v>0.3175775656655666</v>
       </c>
       <c r="CK119" t="n">
         <v>2.93</v>
@@ -34433,7 +34433,7 @@
         <v>41</v>
       </c>
       <c r="CJ120" t="n">
-        <v>1.15</v>
+        <v>1.153999161347288</v>
       </c>
       <c r="CK120" t="n">
         <v>3.77</v>
@@ -34715,7 +34715,7 @@
         <v>58</v>
       </c>
       <c r="CJ121" t="n">
-        <v>0.82</v>
+        <v>0.8235539468961799</v>
       </c>
       <c r="CK121" t="n">
         <v>3.2</v>
@@ -34997,7 +34997,7 @@
         <v>302</v>
       </c>
       <c r="CJ122" t="n">
-        <v>0.41</v>
+        <v>0.413922147077273</v>
       </c>
       <c r="CK122" t="n">
         <v>3.67</v>
@@ -35279,7 +35279,7 @@
         <v>126</v>
       </c>
       <c r="CJ123" t="n">
-        <v>0.47</v>
+        <v>0.4662105103920331</v>
       </c>
       <c r="CK123" t="n">
         <v>2.67</v>
@@ -35561,7 +35561,7 @@
         <v>50</v>
       </c>
       <c r="CJ124" t="n">
-        <v>0.74</v>
+        <v>0.7456299586255907</v>
       </c>
       <c r="CK124" t="n">
         <v>2.69</v>
@@ -35843,7 +35843,7 @@
         <v>126</v>
       </c>
       <c r="CJ125" t="n">
-        <v>0.39</v>
+        <v>0.3858895984892858</v>
       </c>
       <c r="CK125" t="n">
         <v>2.21</v>
@@ -36125,7 +36125,7 @@
         <v>217</v>
       </c>
       <c r="CJ126" t="n">
-        <v>0.33</v>
+        <v>0.3326336743180441</v>
       </c>
       <c r="CK126" t="n">
         <v>2.5</v>
@@ -36407,7 +36407,7 @@
         <v>119</v>
       </c>
       <c r="CJ127" t="n">
-        <v>0.63</v>
+        <v>0.628855168961353</v>
       </c>
       <c r="CK127" t="n">
         <v>3.5</v>
@@ -36689,7 +36689,7 @@
         <v>64</v>
       </c>
       <c r="CJ128" t="n">
-        <v>0.88</v>
+        <v>0.8771</v>
       </c>
       <c r="CK128" t="n">
         <v>3.58</v>
@@ -36971,7 +36971,7 @@
         <v>227</v>
       </c>
       <c r="CJ129" t="n">
-        <v>0.37</v>
+        <v>0.3681540464782724</v>
       </c>
       <c r="CK129" t="n">
         <v>2.83</v>
@@ -37253,7 +37253,7 @@
         <v>271</v>
       </c>
       <c r="CJ130" t="n">
-        <v>0.32</v>
+        <v>0.3226567216098248</v>
       </c>
       <c r="CK130" t="n">
         <v>2.71</v>
@@ -37535,7 +37535,7 @@
         <v>35</v>
       </c>
       <c r="CJ131" t="n">
-        <v>0.68</v>
+        <v>0.6758529544213001</v>
       </c>
       <c r="CK131" t="n">
         <v>2.04</v>
@@ -37817,7 +37817,7 @@
         <v>137</v>
       </c>
       <c r="CJ132" t="n">
-        <v>0.45</v>
+        <v>0.4521260724637098</v>
       </c>
       <c r="CK132" t="n">
         <v>2.7</v>
@@ -38099,7 +38099,7 @@
         <v>363</v>
       </c>
       <c r="CJ133" t="n">
-        <v>0.28</v>
+        <v>0.2798154322821576</v>
       </c>
       <c r="CK133" t="n">
         <v>2.72</v>
@@ -38381,7 +38381,7 @@
         <v>384</v>
       </c>
       <c r="CJ134" t="n">
-        <v>0.3</v>
+        <v>0.2990622851793029</v>
       </c>
       <c r="CK134" t="n">
         <v>2.99</v>
@@ -38663,7 +38663,7 @@
         <v>285</v>
       </c>
       <c r="CJ135" t="n">
-        <v>0.44</v>
+        <v>0.4446644555561954</v>
       </c>
       <c r="CK135" t="n">
         <v>3.83</v>
@@ -38945,7 +38945,7 @@
         <v>183</v>
       </c>
       <c r="CJ136" t="n">
-        <v>0.48</v>
+        <v>0.4766794443623468</v>
       </c>
       <c r="CK136" t="n">
         <v>3.29</v>
@@ -39227,7 +39227,7 @@
         <v>297</v>
       </c>
       <c r="CJ137" t="n">
-        <v>0.41</v>
+        <v>0.4048814173988257</v>
       </c>
       <c r="CK137" t="n">
         <v>3.56</v>
@@ -39509,7 +39509,7 @@
         <v>169</v>
       </c>
       <c r="CJ138" t="n">
-        <v>0.57</v>
+        <v>0.5653846153846154</v>
       </c>
       <c r="CK138" t="n">
         <v>3.75</v>
@@ -39791,7 +39791,7 @@
         <v>297</v>
       </c>
       <c r="CJ139" t="n">
-        <v>0.29</v>
+        <v>0.2911506821744365</v>
       </c>
       <c r="CK139" t="n">
         <v>2.56</v>
@@ -40073,7 +40073,7 @@
         <v>366</v>
       </c>
       <c r="CJ140" t="n">
-        <v>0.3</v>
+        <v>0.2981319479033667</v>
       </c>
       <c r="CK140" t="n">
         <v>2.91</v>
@@ -40355,7 +40355,7 @@
         <v>215</v>
       </c>
       <c r="CJ141" t="n">
-        <v>0.4</v>
+        <v>0.397002544892552</v>
       </c>
       <c r="CK141" t="n">
         <v>2.97</v>
@@ -40637,7 +40637,7 @@
         <v>604</v>
       </c>
       <c r="CJ142" t="n">
-        <v>0.3</v>
+        <v>0.2998647712879968</v>
       </c>
       <c r="CK142" t="n">
         <v>3.76</v>
